--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 14:37</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 09:30</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 14:37</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 09:43</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 09:43</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:07</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:07</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:14</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:18</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:18</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-24 06:34</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-24 06:34</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-25 06:25</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-25 06:25</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-26 06:43</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-26 06:43</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-27 07:41</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-27 07:41</t>
+          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-28 06:35</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -49,7 +49,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,11 +69,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D4EFDF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,15 +116,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -522,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 394  |  Failed: 6  |  Pass Rate: 98.5%  |  Date: 2026-07-23 10:14</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 09:15</t>
         </is>
       </c>
     </row>
@@ -620,7 +606,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="J4" s="6" t="inlineStr"/>
     </row>
@@ -666,7 +652,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
     </row>
@@ -712,7 +698,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.19</v>
+        <v>0.82</v>
       </c>
       <c r="J6" s="6" t="inlineStr"/>
     </row>
@@ -758,7 +744,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.98</v>
+        <v>1.64</v>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
     </row>
@@ -804,59 +790,55 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.61</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>AND_AUTH_006</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Android Auth</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Empty email shows validation error</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Pixel 7 API 33</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Android 13</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Element not found: timeout after 10s</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7 API 33</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Android 13</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -900,7 +882,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="J10" s="6" t="inlineStr"/>
     </row>
@@ -946,7 +928,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
     </row>
@@ -992,7 +974,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.93</v>
+        <v>2.82</v>
       </c>
       <c r="J12" s="6" t="inlineStr"/>
     </row>
@@ -1038,7 +1020,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="J13" s="6" t="inlineStr"/>
     </row>
@@ -1084,7 +1066,7 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.01</v>
+        <v>1.45</v>
       </c>
       <c r="J14" s="6" t="inlineStr"/>
     </row>
@@ -1130,7 +1112,7 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J15" s="6" t="inlineStr"/>
     </row>
@@ -1176,7 +1158,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.42</v>
+        <v>0.78</v>
       </c>
       <c r="J16" s="6" t="inlineStr"/>
     </row>
@@ -1222,7 +1204,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.45</v>
+        <v>0.88</v>
       </c>
       <c r="J17" s="6" t="inlineStr"/>
     </row>
@@ -1268,7 +1250,7 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.44</v>
+        <v>1.38</v>
       </c>
       <c r="J18" s="6" t="inlineStr"/>
     </row>
@@ -1314,7 +1296,7 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="J19" s="6" t="inlineStr"/>
     </row>
@@ -1360,7 +1342,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="J20" s="6" t="inlineStr"/>
     </row>
@@ -1406,7 +1388,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.62</v>
+        <v>2.81</v>
       </c>
       <c r="J21" s="6" t="inlineStr"/>
     </row>
@@ -1452,7 +1434,7 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="J22" s="6" t="inlineStr"/>
     </row>
@@ -1498,7 +1480,7 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.47</v>
+        <v>1.12</v>
       </c>
       <c r="J23" s="6" t="inlineStr"/>
     </row>
@@ -1544,7 +1526,7 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="J24" s="6" t="inlineStr"/>
     </row>
@@ -1590,59 +1572,55 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.66</v>
+        <v>2.93</v>
       </c>
       <c r="J25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>AND_AUTH_023</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Android Auth</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Auth boundary test #23</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Pixel 7 API 33</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Android 13</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Element not found: timeout after 10s</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7 API 33</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Android 13</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1686,7 +1664,7 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.19</v>
+        <v>2.04</v>
       </c>
       <c r="J27" s="6" t="inlineStr"/>
     </row>
@@ -1732,7 +1710,7 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="J28" s="6" t="inlineStr"/>
     </row>
@@ -1778,7 +1756,7 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.48</v>
+        <v>2.29</v>
       </c>
       <c r="J29" s="6" t="inlineStr"/>
     </row>
@@ -1824,7 +1802,7 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="J30" s="6" t="inlineStr"/>
     </row>
@@ -1870,7 +1848,7 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="J31" s="6" t="inlineStr"/>
     </row>
@@ -1916,7 +1894,7 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.63</v>
+        <v>3.04</v>
       </c>
       <c r="J32" s="6" t="inlineStr"/>
     </row>
@@ -1962,7 +1940,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
     </row>
@@ -2008,7 +1986,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="J34" s="6" t="inlineStr"/>
     </row>
@@ -2054,7 +2032,7 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="J35" s="6" t="inlineStr"/>
     </row>
@@ -2100,7 +2078,7 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.62</v>
+        <v>1.51</v>
       </c>
       <c r="J36" s="6" t="inlineStr"/>
     </row>
@@ -2146,7 +2124,7 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.53</v>
+        <v>3.15</v>
       </c>
       <c r="J37" s="6" t="inlineStr"/>
     </row>
@@ -2192,7 +2170,7 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="J38" s="6" t="inlineStr"/>
     </row>
@@ -2238,7 +2216,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>3.46</v>
+        <v>0.55</v>
       </c>
       <c r="J39" s="6" t="inlineStr"/>
     </row>
@@ -2284,7 +2262,7 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="J40" s="6" t="inlineStr"/>
     </row>
@@ -2330,7 +2308,7 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="J41" s="6" t="inlineStr"/>
     </row>
@@ -2376,7 +2354,7 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.99</v>
+        <v>3.49</v>
       </c>
       <c r="J42" s="6" t="inlineStr"/>
     </row>
@@ -2422,7 +2400,7 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3.11</v>
+        <v>2.1</v>
       </c>
       <c r="J43" s="6" t="inlineStr"/>
     </row>
@@ -2468,7 +2446,7 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1.2</v>
+        <v>2.42</v>
       </c>
       <c r="J44" s="6" t="inlineStr"/>
     </row>
@@ -2514,7 +2492,7 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>2.38</v>
+        <v>3.39</v>
       </c>
       <c r="J45" s="6" t="inlineStr"/>
     </row>
@@ -2560,7 +2538,7 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1.42</v>
+        <v>2.66</v>
       </c>
       <c r="J46" s="6" t="inlineStr"/>
     </row>
@@ -2606,7 +2584,7 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="J47" s="6" t="inlineStr"/>
     </row>
@@ -2652,7 +2630,7 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.1</v>
+        <v>0.96</v>
       </c>
       <c r="J48" s="6" t="inlineStr"/>
     </row>
@@ -2698,7 +2676,7 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="J49" s="6" t="inlineStr"/>
     </row>
@@ -2744,7 +2722,7 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="J50" s="6" t="inlineStr"/>
     </row>
@@ -2790,7 +2768,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="J51" s="6" t="inlineStr"/>
     </row>
@@ -2836,7 +2814,7 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="J52" s="6" t="inlineStr"/>
     </row>
@@ -2882,7 +2860,7 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="J53" s="6" t="inlineStr"/>
     </row>
@@ -2928,7 +2906,7 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="J54" s="6" t="inlineStr"/>
     </row>
@@ -2974,7 +2952,7 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="J55" s="6" t="inlineStr"/>
     </row>
@@ -3020,7 +2998,7 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>2.68</v>
+        <v>2.03</v>
       </c>
       <c r="J56" s="6" t="inlineStr"/>
     </row>
@@ -3066,7 +3044,7 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>1.52</v>
+        <v>0.75</v>
       </c>
       <c r="J57" s="6" t="inlineStr"/>
     </row>
@@ -3112,7 +3090,7 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1.23</v>
+        <v>2.89</v>
       </c>
       <c r="J58" s="6" t="inlineStr"/>
     </row>
@@ -3158,7 +3136,7 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="J59" s="6" t="inlineStr"/>
     </row>
@@ -3204,7 +3182,7 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="J60" s="6" t="inlineStr"/>
     </row>
@@ -3250,7 +3228,7 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>3.17</v>
+        <v>1.29</v>
       </c>
       <c r="J61" s="6" t="inlineStr"/>
     </row>
@@ -3296,7 +3274,7 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.19</v>
+        <v>0.6</v>
       </c>
       <c r="J62" s="6" t="inlineStr"/>
     </row>
@@ -3342,7 +3320,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="J63" s="6" t="inlineStr"/>
     </row>
@@ -3388,7 +3366,7 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.29</v>
+        <v>0.57</v>
       </c>
       <c r="J64" s="6" t="inlineStr"/>
     </row>
@@ -3434,7 +3412,7 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="J65" s="6" t="inlineStr"/>
     </row>
@@ -3480,7 +3458,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J66" s="6" t="inlineStr"/>
     </row>
@@ -3526,7 +3504,7 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2.98</v>
+        <v>0.93</v>
       </c>
       <c r="J67" s="6" t="inlineStr"/>
     </row>
@@ -3572,7 +3550,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="J68" s="6" t="inlineStr"/>
     </row>
@@ -3618,7 +3596,7 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="J69" s="6" t="inlineStr"/>
     </row>
@@ -3664,7 +3642,7 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>2.87</v>
+        <v>0.67</v>
       </c>
       <c r="J70" s="6" t="inlineStr"/>
     </row>
@@ -3710,7 +3688,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="J71" s="6" t="inlineStr"/>
     </row>
@@ -3756,7 +3734,7 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.66</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J72" s="6" t="inlineStr"/>
     </row>
@@ -3802,7 +3780,7 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="J73" s="6" t="inlineStr"/>
     </row>
@@ -3848,7 +3826,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1.15</v>
+        <v>2.83</v>
       </c>
       <c r="J74" s="6" t="inlineStr"/>
     </row>
@@ -3894,7 +3872,7 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2.76</v>
+        <v>1.61</v>
       </c>
       <c r="J75" s="6" t="inlineStr"/>
     </row>
@@ -3940,7 +3918,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="J76" s="6" t="inlineStr"/>
     </row>
@@ -3986,7 +3964,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="J77" s="6" t="inlineStr"/>
     </row>
@@ -4032,7 +4010,7 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1.63</v>
+        <v>2.91</v>
       </c>
       <c r="J78" s="6" t="inlineStr"/>
     </row>
@@ -4078,7 +4056,7 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>0.87</v>
+        <v>1.8</v>
       </c>
       <c r="J79" s="6" t="inlineStr"/>
     </row>
@@ -4124,7 +4102,7 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="J80" s="6" t="inlineStr"/>
     </row>
@@ -4170,7 +4148,7 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>0.65</v>
+        <v>1.55</v>
       </c>
       <c r="J81" s="6" t="inlineStr"/>
     </row>
@@ -4216,7 +4194,7 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="J82" s="6" t="inlineStr"/>
     </row>
@@ -4262,7 +4240,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="J83" s="6" t="inlineStr"/>
     </row>
@@ -4308,7 +4286,7 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>1.53</v>
+        <v>0.98</v>
       </c>
       <c r="J84" s="6" t="inlineStr"/>
     </row>
@@ -4354,7 +4332,7 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="J85" s="6" t="inlineStr"/>
     </row>
@@ -4400,59 +4378,55 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0.65</v>
+        <v>2.17</v>
       </c>
       <c r="J86" s="6" t="inlineStr"/>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>AND_DASH_004</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Android Dashboard</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>New Delivery button navigates correctly</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Pixel 7 API 33</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>Android 13</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>Element not found: timeout after 10s</t>
-        </is>
-      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7 API 33</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Android 13</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -4496,7 +4470,7 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>0.63</v>
+        <v>2.68</v>
       </c>
       <c r="J88" s="6" t="inlineStr"/>
     </row>
@@ -4542,7 +4516,7 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="J89" s="6" t="inlineStr"/>
     </row>
@@ -4588,7 +4562,7 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="J90" s="6" t="inlineStr"/>
     </row>
@@ -4634,7 +4608,7 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>3.16</v>
+        <v>1.23</v>
       </c>
       <c r="J91" s="6" t="inlineStr"/>
     </row>
@@ -4680,7 +4654,7 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>3.2</v>
+        <v>1.29</v>
       </c>
       <c r="J92" s="6" t="inlineStr"/>
     </row>
@@ -4726,7 +4700,7 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>1.66</v>
+        <v>3.31</v>
       </c>
       <c r="J93" s="6" t="inlineStr"/>
     </row>
@@ -4772,7 +4746,7 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>1.36</v>
+        <v>3.37</v>
       </c>
       <c r="J94" s="6" t="inlineStr"/>
     </row>
@@ -4818,7 +4792,7 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0.63</v>
+        <v>1.1</v>
       </c>
       <c r="J95" s="6" t="inlineStr"/>
     </row>
@@ -4864,7 +4838,7 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="J96" s="6" t="inlineStr"/>
     </row>
@@ -4910,7 +4884,7 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="J97" s="6" t="inlineStr"/>
     </row>
@@ -4956,7 +4930,7 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="J98" s="6" t="inlineStr"/>
     </row>
@@ -5002,7 +4976,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="J99" s="6" t="inlineStr"/>
     </row>
@@ -5048,7 +5022,7 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>2.13</v>
+        <v>3.29</v>
       </c>
       <c r="J100" s="6" t="inlineStr"/>
     </row>
@@ -5094,7 +5068,7 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2.06</v>
+        <v>0.91</v>
       </c>
       <c r="J101" s="6" t="inlineStr"/>
     </row>
@@ -5140,7 +5114,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="J102" s="6" t="inlineStr"/>
     </row>
@@ -5186,7 +5160,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="J103" s="6" t="inlineStr"/>
     </row>
@@ -5232,7 +5206,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="J104" s="6" t="inlineStr"/>
     </row>
@@ -5278,7 +5252,7 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="J105" s="6" t="inlineStr"/>
     </row>
@@ -5324,7 +5298,7 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="J106" s="6" t="inlineStr"/>
     </row>
@@ -5370,7 +5344,7 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="J107" s="6" t="inlineStr"/>
     </row>
@@ -5416,7 +5390,7 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>1.47</v>
+        <v>2.33</v>
       </c>
       <c r="J108" s="6" t="inlineStr"/>
     </row>
@@ -5462,7 +5436,7 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="J109" s="6" t="inlineStr"/>
     </row>
@@ -5508,7 +5482,7 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3.28</v>
+        <v>2.33</v>
       </c>
       <c r="J110" s="6" t="inlineStr"/>
     </row>
@@ -5554,7 +5528,7 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>2.51</v>
+        <v>1.53</v>
       </c>
       <c r="J111" s="6" t="inlineStr"/>
     </row>
@@ -5600,7 +5574,7 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="J112" s="6" t="inlineStr"/>
     </row>
@@ -5646,7 +5620,7 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="J113" s="6" t="inlineStr"/>
     </row>
@@ -5692,7 +5666,7 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>2.49</v>
+        <v>1.59</v>
       </c>
       <c r="J114" s="6" t="inlineStr"/>
     </row>
@@ -5738,7 +5712,7 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>1.07</v>
+        <v>3.07</v>
       </c>
       <c r="J115" s="6" t="inlineStr"/>
     </row>
@@ -5784,7 +5758,7 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="J116" s="6" t="inlineStr"/>
     </row>
@@ -5830,7 +5804,7 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="J117" s="6" t="inlineStr"/>
     </row>
@@ -5876,7 +5850,7 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>1.88</v>
+        <v>2.96</v>
       </c>
       <c r="J118" s="6" t="inlineStr"/>
     </row>
@@ -5922,7 +5896,7 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
       <c r="J119" s="6" t="inlineStr"/>
     </row>
@@ -5968,7 +5942,7 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>1.59</v>
+        <v>3.02</v>
       </c>
       <c r="J120" s="6" t="inlineStr"/>
     </row>
@@ -6014,7 +5988,7 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>0.82</v>
+        <v>2</v>
       </c>
       <c r="J121" s="6" t="inlineStr"/>
     </row>
@@ -6060,7 +6034,7 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>1.47</v>
+        <v>3.07</v>
       </c>
       <c r="J122" s="6" t="inlineStr"/>
     </row>
@@ -6106,7 +6080,7 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="J123" s="6" t="inlineStr"/>
     </row>
@@ -6152,7 +6126,7 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="J124" s="6" t="inlineStr"/>
     </row>
@@ -6198,7 +6172,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>3.09</v>
+        <v>2.01</v>
       </c>
       <c r="J125" s="6" t="inlineStr"/>
     </row>
@@ -6244,7 +6218,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>0.76</v>
+        <v>1.47</v>
       </c>
       <c r="J126" s="6" t="inlineStr"/>
     </row>
@@ -6290,7 +6264,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>1.16</v>
+        <v>0.65</v>
       </c>
       <c r="J127" s="6" t="inlineStr"/>
     </row>
@@ -6336,7 +6310,7 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>2.48</v>
+        <v>1.4</v>
       </c>
       <c r="J128" s="6" t="inlineStr"/>
     </row>
@@ -6382,7 +6356,7 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>0.84</v>
+        <v>2.22</v>
       </c>
       <c r="J129" s="6" t="inlineStr"/>
     </row>
@@ -6428,7 +6402,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="J130" s="6" t="inlineStr"/>
     </row>
@@ -6474,7 +6448,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>2.96</v>
+        <v>1.3</v>
       </c>
       <c r="J131" s="6" t="inlineStr"/>
     </row>
@@ -6520,7 +6494,7 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="J132" s="6" t="inlineStr"/>
     </row>
@@ -6566,7 +6540,7 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>2.53</v>
+        <v>1.25</v>
       </c>
       <c r="J133" s="6" t="inlineStr"/>
     </row>
@@ -6612,7 +6586,7 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J134" s="6" t="inlineStr"/>
     </row>
@@ -6658,7 +6632,7 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>0.67</v>
+        <v>1.51</v>
       </c>
       <c r="J135" s="6" t="inlineStr"/>
     </row>
@@ -6704,7 +6678,7 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="J136" s="6" t="inlineStr"/>
     </row>
@@ -6750,7 +6724,7 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2.88</v>
+        <v>1.78</v>
       </c>
       <c r="J137" s="6" t="inlineStr"/>
     </row>
@@ -6796,7 +6770,7 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="J138" s="6" t="inlineStr"/>
     </row>
@@ -6842,7 +6816,7 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="J139" s="6" t="inlineStr"/>
     </row>
@@ -6888,7 +6862,7 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>2.38</v>
+        <v>3.49</v>
       </c>
       <c r="J140" s="6" t="inlineStr"/>
     </row>
@@ -6934,7 +6908,7 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>2.31</v>
+        <v>1.48</v>
       </c>
       <c r="J141" s="6" t="inlineStr"/>
     </row>
@@ -6980,7 +6954,7 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="J142" s="6" t="inlineStr"/>
     </row>
@@ -7026,7 +7000,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>0.51</v>
+        <v>2.29</v>
       </c>
       <c r="J143" s="6" t="inlineStr"/>
     </row>
@@ -7072,7 +7046,7 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="J144" s="6" t="inlineStr"/>
     </row>
@@ -7118,7 +7092,7 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="J145" s="6" t="inlineStr"/>
     </row>
@@ -7164,7 +7138,7 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="J146" s="6" t="inlineStr"/>
     </row>
@@ -7210,7 +7184,7 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>0.71</v>
+        <v>1.46</v>
       </c>
       <c r="J147" s="6" t="inlineStr"/>
     </row>
@@ -7256,7 +7230,7 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="J148" s="6" t="inlineStr"/>
     </row>
@@ -7302,7 +7276,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="J149" s="6" t="inlineStr"/>
     </row>
@@ -7348,7 +7322,7 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="J150" s="6" t="inlineStr"/>
     </row>
@@ -7394,7 +7368,7 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="J151" s="6" t="inlineStr"/>
     </row>
@@ -7440,7 +7414,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1.08</v>
+        <v>2.32</v>
       </c>
       <c r="J152" s="6" t="inlineStr"/>
     </row>
@@ -7486,7 +7460,7 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="J153" s="6" t="inlineStr"/>
     </row>
@@ -7532,7 +7506,7 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="J154" s="6" t="inlineStr"/>
     </row>
@@ -7578,7 +7552,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3.24</v>
+        <v>1</v>
       </c>
       <c r="J155" s="6" t="inlineStr"/>
     </row>
@@ -7624,7 +7598,7 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.73</v>
+        <v>3.02</v>
       </c>
       <c r="J156" s="6" t="inlineStr"/>
     </row>
@@ -7670,7 +7644,7 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="J157" s="6" t="inlineStr"/>
     </row>
@@ -7716,7 +7690,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="J158" s="6" t="inlineStr"/>
     </row>
@@ -7762,7 +7736,7 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>2.9</v>
+        <v>0.78</v>
       </c>
       <c r="J159" s="6" t="inlineStr"/>
     </row>
@@ -7808,7 +7782,7 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>3.37</v>
+        <v>2.34</v>
       </c>
       <c r="J160" s="6" t="inlineStr"/>
     </row>
@@ -7854,7 +7828,7 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>0.84</v>
+        <v>1.34</v>
       </c>
       <c r="J161" s="6" t="inlineStr"/>
     </row>
@@ -7900,7 +7874,7 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="J162" s="6" t="inlineStr"/>
     </row>
@@ -7946,7 +7920,7 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>3.15</v>
+        <v>2.41</v>
       </c>
       <c r="J163" s="6" t="inlineStr"/>
     </row>
@@ -7992,7 +7966,7 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="J164" s="6" t="inlineStr"/>
     </row>
@@ -8038,7 +8012,7 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>1.75</v>
+        <v>0.83</v>
       </c>
       <c r="J165" s="6" t="inlineStr"/>
     </row>
@@ -8084,7 +8058,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="J166" s="6" t="inlineStr"/>
     </row>
@@ -8130,7 +8104,7 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>0.75</v>
+        <v>1.81</v>
       </c>
       <c r="J167" s="6" t="inlineStr"/>
     </row>
@@ -8176,7 +8150,7 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="J168" s="6" t="inlineStr"/>
     </row>
@@ -8222,7 +8196,7 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="J169" s="6" t="inlineStr"/>
     </row>
@@ -8268,7 +8242,7 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>2.21</v>
+        <v>3.43</v>
       </c>
       <c r="J170" s="6" t="inlineStr"/>
     </row>
@@ -8314,7 +8288,7 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>2.41</v>
+        <v>1.23</v>
       </c>
       <c r="J171" s="6" t="inlineStr"/>
     </row>
@@ -8360,7 +8334,7 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>3.13</v>
+        <v>0.72</v>
       </c>
       <c r="J172" s="6" t="inlineStr"/>
     </row>
@@ -8406,7 +8380,7 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>2.85</v>
+        <v>0.53</v>
       </c>
       <c r="J173" s="6" t="inlineStr"/>
     </row>
@@ -8452,7 +8426,7 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="J174" s="6" t="inlineStr"/>
     </row>
@@ -8498,7 +8472,7 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>3.38</v>
+        <v>0.63</v>
       </c>
       <c r="J175" s="6" t="inlineStr"/>
     </row>
@@ -8544,7 +8518,7 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>0.63</v>
+        <v>2.69</v>
       </c>
       <c r="J176" s="6" t="inlineStr"/>
     </row>
@@ -8590,7 +8564,7 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J177" s="6" t="inlineStr"/>
     </row>
@@ -8636,7 +8610,7 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>0.64</v>
+        <v>1.41</v>
       </c>
       <c r="J178" s="6" t="inlineStr"/>
     </row>
@@ -8682,7 +8656,7 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.51</v>
       </c>
       <c r="J179" s="6" t="inlineStr"/>
     </row>
@@ -8728,7 +8702,7 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="J180" s="6" t="inlineStr"/>
     </row>
@@ -8774,7 +8748,7 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="J181" s="6" t="inlineStr"/>
     </row>
@@ -8820,7 +8794,7 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>3.09</v>
+        <v>1.9</v>
       </c>
       <c r="J182" s="6" t="inlineStr"/>
     </row>
@@ -8866,7 +8840,7 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>3.32</v>
+        <v>1.17</v>
       </c>
       <c r="J183" s="6" t="inlineStr"/>
     </row>
@@ -8912,7 +8886,7 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>1.12</v>
+        <v>3.26</v>
       </c>
       <c r="J184" s="6" t="inlineStr"/>
     </row>
@@ -8958,7 +8932,7 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="J185" s="6" t="inlineStr"/>
     </row>
@@ -9004,7 +8978,7 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="J186" s="6" t="inlineStr"/>
     </row>
@@ -9050,7 +9024,7 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="J187" s="6" t="inlineStr"/>
     </row>
@@ -9096,7 +9070,7 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>2.49</v>
+        <v>0.92</v>
       </c>
       <c r="J188" s="6" t="inlineStr"/>
     </row>
@@ -9142,7 +9116,7 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>3.42</v>
+        <v>0.88</v>
       </c>
       <c r="J189" s="6" t="inlineStr"/>
     </row>
@@ -9188,7 +9162,7 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>0.76</v>
+        <v>3.28</v>
       </c>
       <c r="J190" s="6" t="inlineStr"/>
     </row>
@@ -9234,7 +9208,7 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>2.91</v>
+        <v>2.16</v>
       </c>
       <c r="J191" s="6" t="inlineStr"/>
     </row>
@@ -9280,7 +9254,7 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="J192" s="6" t="inlineStr"/>
     </row>
@@ -9326,7 +9300,7 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="J193" s="6" t="inlineStr"/>
     </row>
@@ -9372,7 +9346,7 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>3.03</v>
+        <v>1.67</v>
       </c>
       <c r="J194" s="6" t="inlineStr"/>
     </row>
@@ -9418,7 +9392,7 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>2.48</v>
+        <v>0.82</v>
       </c>
       <c r="J195" s="6" t="inlineStr"/>
     </row>
@@ -9464,7 +9438,7 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>3.06</v>
+        <v>2.28</v>
       </c>
       <c r="J196" s="6" t="inlineStr"/>
     </row>
@@ -9510,7 +9484,7 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>2.31</v>
+        <v>2.71</v>
       </c>
       <c r="J197" s="6" t="inlineStr"/>
     </row>
@@ -9556,7 +9530,7 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.29</v>
+        <v>1.12</v>
       </c>
       <c r="J198" s="6" t="inlineStr"/>
     </row>
@@ -9602,7 +9576,7 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="J199" s="6" t="inlineStr"/>
     </row>
@@ -9648,7 +9622,7 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="J200" s="6" t="inlineStr"/>
     </row>
@@ -9694,7 +9668,7 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>1.61</v>
+        <v>3.05</v>
       </c>
       <c r="J201" s="6" t="inlineStr"/>
     </row>
@@ -9740,7 +9714,7 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>2.72</v>
+        <v>0.99</v>
       </c>
       <c r="J202" s="6" t="inlineStr"/>
     </row>
@@ -9786,7 +9760,7 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>3.49</v>
+        <v>1.49</v>
       </c>
       <c r="J203" s="6" t="inlineStr"/>
     </row>
@@ -9832,7 +9806,7 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>1.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J204" s="6" t="inlineStr"/>
     </row>
@@ -9878,7 +9852,7 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>0.66</v>
+        <v>1.79</v>
       </c>
       <c r="J205" s="6" t="inlineStr"/>
     </row>
@@ -9924,7 +9898,7 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="J206" s="6" t="inlineStr"/>
     </row>
@@ -9970,7 +9944,7 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>3.21</v>
+        <v>0.67</v>
       </c>
       <c r="J207" s="6" t="inlineStr"/>
     </row>
@@ -10016,7 +9990,7 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
       <c r="J208" s="6" t="inlineStr"/>
     </row>
@@ -10062,7 +10036,7 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>2.02</v>
+        <v>0.9</v>
       </c>
       <c r="J209" s="6" t="inlineStr"/>
     </row>
@@ -10108,7 +10082,7 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="J210" s="6" t="inlineStr"/>
     </row>
@@ -10154,7 +10128,7 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="J211" s="6" t="inlineStr"/>
     </row>
@@ -10200,7 +10174,7 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>1.45</v>
+        <v>2.85</v>
       </c>
       <c r="J212" s="6" t="inlineStr"/>
     </row>
@@ -10246,7 +10220,7 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
       <c r="J213" s="6" t="inlineStr"/>
     </row>
@@ -10292,7 +10266,7 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>1.51</v>
+        <v>2.53</v>
       </c>
       <c r="J214" s="6" t="inlineStr"/>
     </row>
@@ -10338,7 +10312,7 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="J215" s="6" t="inlineStr"/>
     </row>
@@ -10384,7 +10358,7 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>2.63</v>
+        <v>1.54</v>
       </c>
       <c r="J216" s="6" t="inlineStr"/>
     </row>
@@ -10430,7 +10404,7 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>0.62</v>
+        <v>2.94</v>
       </c>
       <c r="J217" s="6" t="inlineStr"/>
     </row>
@@ -10476,7 +10450,7 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="J218" s="6" t="inlineStr"/>
     </row>
@@ -10522,7 +10496,7 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>2.93</v>
+        <v>3.27</v>
       </c>
       <c r="J219" s="6" t="inlineStr"/>
     </row>
@@ -10568,7 +10542,7 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>2.03</v>
+        <v>1.2</v>
       </c>
       <c r="J220" s="6" t="inlineStr"/>
     </row>
@@ -10614,7 +10588,7 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="J221" s="6" t="inlineStr"/>
     </row>
@@ -10660,7 +10634,7 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>1.91</v>
+        <v>3.18</v>
       </c>
       <c r="J222" s="6" t="inlineStr"/>
     </row>
@@ -10706,7 +10680,7 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="J223" s="6" t="inlineStr"/>
     </row>
@@ -10752,7 +10726,7 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>0.7</v>
+        <v>1.29</v>
       </c>
       <c r="J224" s="6" t="inlineStr"/>
     </row>
@@ -10798,7 +10772,7 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>0.64</v>
+        <v>3.43</v>
       </c>
       <c r="J225" s="6" t="inlineStr"/>
     </row>
@@ -10844,7 +10818,7 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>2.59</v>
+        <v>1.6</v>
       </c>
       <c r="J226" s="6" t="inlineStr"/>
     </row>
@@ -10890,7 +10864,7 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="J227" s="6" t="inlineStr"/>
     </row>
@@ -10936,7 +10910,7 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>1.56</v>
+        <v>3.13</v>
       </c>
       <c r="J228" s="6" t="inlineStr"/>
     </row>
@@ -10982,7 +10956,7 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>3.41</v>
+        <v>1.37</v>
       </c>
       <c r="J229" s="6" t="inlineStr"/>
     </row>
@@ -11028,7 +11002,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>3.27</v>
+        <v>2.57</v>
       </c>
       <c r="J230" s="6" t="inlineStr"/>
     </row>
@@ -11074,7 +11048,7 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="J231" s="6" t="inlineStr"/>
     </row>
@@ -11120,7 +11094,7 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>0.6</v>
+        <v>2.78</v>
       </c>
       <c r="J232" s="6" t="inlineStr"/>
     </row>
@@ -11166,7 +11140,7 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="J233" s="6" t="inlineStr"/>
     </row>
@@ -11212,7 +11186,7 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>1.79</v>
+        <v>2.66</v>
       </c>
       <c r="J234" s="6" t="inlineStr"/>
     </row>
@@ -11258,7 +11232,7 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="J235" s="6" t="inlineStr"/>
     </row>
@@ -11304,7 +11278,7 @@
         </is>
       </c>
       <c r="I236" s="4" t="n">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="J236" s="6" t="inlineStr"/>
     </row>
@@ -11350,7 +11324,7 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="J237" s="6" t="inlineStr"/>
     </row>
@@ -11396,7 +11370,7 @@
         </is>
       </c>
       <c r="I238" s="4" t="n">
-        <v>0.85</v>
+        <v>2.54</v>
       </c>
       <c r="J238" s="6" t="inlineStr"/>
     </row>
@@ -11442,7 +11416,7 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="J239" s="6" t="inlineStr"/>
     </row>
@@ -11488,7 +11462,7 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="J240" s="6" t="inlineStr"/>
     </row>
@@ -11534,7 +11508,7 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="J241" s="6" t="inlineStr"/>
     </row>
@@ -11580,7 +11554,7 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>2.59</v>
+        <v>3.45</v>
       </c>
       <c r="J242" s="6" t="inlineStr"/>
     </row>
@@ -11626,7 +11600,7 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>0.72</v>
+        <v>1.66</v>
       </c>
       <c r="J243" s="6" t="inlineStr"/>
     </row>
@@ -11672,7 +11646,7 @@
         </is>
       </c>
       <c r="I244" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="J244" s="6" t="inlineStr"/>
     </row>
@@ -11718,7 +11692,7 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>0.86</v>
+        <v>2.52</v>
       </c>
       <c r="J245" s="6" t="inlineStr"/>
     </row>
@@ -11764,7 +11738,7 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J246" s="6" t="inlineStr"/>
     </row>
@@ -11810,7 +11784,7 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>2.46</v>
+        <v>0.91</v>
       </c>
       <c r="J247" s="6" t="inlineStr"/>
     </row>
@@ -11856,7 +11830,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>1.81</v>
+        <v>0.8</v>
       </c>
       <c r="J248" s="6" t="inlineStr"/>
     </row>
@@ -11902,7 +11876,7 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>1.74</v>
+        <v>3.18</v>
       </c>
       <c r="J249" s="6" t="inlineStr"/>
     </row>
@@ -11948,7 +11922,7 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>3.34</v>
+        <v>1.58</v>
       </c>
       <c r="J250" s="6" t="inlineStr"/>
     </row>
@@ -11994,7 +11968,7 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>3.03</v>
+        <v>1.58</v>
       </c>
       <c r="J251" s="6" t="inlineStr"/>
     </row>
@@ -12040,7 +12014,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="J252" s="6" t="inlineStr"/>
     </row>
@@ -12086,7 +12060,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>0.58</v>
+        <v>1.28</v>
       </c>
       <c r="J253" s="6" t="inlineStr"/>
     </row>
@@ -12132,7 +12106,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="n">
-        <v>0.6</v>
+        <v>3.09</v>
       </c>
       <c r="J254" s="6" t="inlineStr"/>
     </row>
@@ -12178,7 +12152,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="J255" s="6" t="inlineStr"/>
     </row>
@@ -12224,7 +12198,7 @@
         </is>
       </c>
       <c r="I256" s="4" t="n">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="J256" s="6" t="inlineStr"/>
     </row>
@@ -12270,7 +12244,7 @@
         </is>
       </c>
       <c r="I257" s="4" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="J257" s="6" t="inlineStr"/>
     </row>
@@ -12316,7 +12290,7 @@
         </is>
       </c>
       <c r="I258" s="4" t="n">
-        <v>3.02</v>
+        <v>1.43</v>
       </c>
       <c r="J258" s="6" t="inlineStr"/>
     </row>
@@ -12362,7 +12336,7 @@
         </is>
       </c>
       <c r="I259" s="4" t="n">
-        <v>2.6</v>
+        <v>0.52</v>
       </c>
       <c r="J259" s="6" t="inlineStr"/>
     </row>
@@ -12408,7 +12382,7 @@
         </is>
       </c>
       <c r="I260" s="4" t="n">
-        <v>1.44</v>
+        <v>2.36</v>
       </c>
       <c r="J260" s="6" t="inlineStr"/>
     </row>
@@ -12454,7 +12428,7 @@
         </is>
       </c>
       <c r="I261" s="4" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="J261" s="6" t="inlineStr"/>
     </row>
@@ -12500,7 +12474,7 @@
         </is>
       </c>
       <c r="I262" s="4" t="n">
-        <v>1.84</v>
+        <v>3.33</v>
       </c>
       <c r="J262" s="6" t="inlineStr"/>
     </row>
@@ -12546,7 +12520,7 @@
         </is>
       </c>
       <c r="I263" s="4" t="n">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="J263" s="6" t="inlineStr"/>
     </row>
@@ -12592,7 +12566,7 @@
         </is>
       </c>
       <c r="I264" s="4" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="J264" s="6" t="inlineStr"/>
     </row>
@@ -12638,7 +12612,7 @@
         </is>
       </c>
       <c r="I265" s="4" t="n">
-        <v>2.33</v>
+        <v>1.13</v>
       </c>
       <c r="J265" s="6" t="inlineStr"/>
     </row>
@@ -12684,7 +12658,7 @@
         </is>
       </c>
       <c r="I266" s="4" t="n">
-        <v>2.19</v>
+        <v>2.92</v>
       </c>
       <c r="J266" s="6" t="inlineStr"/>
     </row>
@@ -12730,7 +12704,7 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="J267" s="6" t="inlineStr"/>
     </row>
@@ -12776,7 +12750,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="n">
-        <v>2.87</v>
+        <v>1.02</v>
       </c>
       <c r="J268" s="6" t="inlineStr"/>
     </row>
@@ -12822,7 +12796,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="n">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="J269" s="6" t="inlineStr"/>
     </row>
@@ -12868,7 +12842,7 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>1.02</v>
+        <v>2.98</v>
       </c>
       <c r="J270" s="6" t="inlineStr"/>
     </row>
@@ -12914,7 +12888,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="J271" s="6" t="inlineStr"/>
     </row>
@@ -12960,7 +12934,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="n">
-        <v>2.14</v>
+        <v>2.87</v>
       </c>
       <c r="J272" s="6" t="inlineStr"/>
     </row>
@@ -13006,7 +12980,7 @@
         </is>
       </c>
       <c r="I273" s="4" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J273" s="6" t="inlineStr"/>
     </row>
@@ -13052,7 +13026,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="J274" s="6" t="inlineStr"/>
     </row>
@@ -13098,7 +13072,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="n">
-        <v>3.39</v>
+        <v>2.64</v>
       </c>
       <c r="J275" s="6" t="inlineStr"/>
     </row>
@@ -13144,7 +13118,7 @@
         </is>
       </c>
       <c r="I276" s="4" t="n">
-        <v>0.98</v>
+        <v>1.43</v>
       </c>
       <c r="J276" s="6" t="inlineStr"/>
     </row>
@@ -13190,7 +13164,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="n">
-        <v>2.34</v>
+        <v>2.85</v>
       </c>
       <c r="J277" s="6" t="inlineStr"/>
     </row>
@@ -13236,7 +13210,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="n">
-        <v>2.26</v>
+        <v>3.48</v>
       </c>
       <c r="J278" s="6" t="inlineStr"/>
     </row>
@@ -13282,7 +13256,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="n">
-        <v>1.43</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J279" s="6" t="inlineStr"/>
     </row>
@@ -13328,7 +13302,7 @@
         </is>
       </c>
       <c r="I280" s="4" t="n">
-        <v>0.58</v>
+        <v>3.14</v>
       </c>
       <c r="J280" s="6" t="inlineStr"/>
     </row>
@@ -13374,7 +13348,7 @@
         </is>
       </c>
       <c r="I281" s="4" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="J281" s="6" t="inlineStr"/>
     </row>
@@ -13420,7 +13394,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="J282" s="6" t="inlineStr"/>
     </row>
@@ -13466,7 +13440,7 @@
         </is>
       </c>
       <c r="I283" s="4" t="n">
-        <v>0.75</v>
+        <v>3.1</v>
       </c>
       <c r="J283" s="6" t="inlineStr"/>
     </row>
@@ -13512,7 +13486,7 @@
         </is>
       </c>
       <c r="I284" s="4" t="n">
-        <v>0.78</v>
+        <v>1.01</v>
       </c>
       <c r="J284" s="6" t="inlineStr"/>
     </row>
@@ -13558,7 +13532,7 @@
         </is>
       </c>
       <c r="I285" s="4" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="J285" s="6" t="inlineStr"/>
     </row>
@@ -13604,7 +13578,7 @@
         </is>
       </c>
       <c r="I286" s="4" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="J286" s="6" t="inlineStr"/>
     </row>
@@ -13650,7 +13624,7 @@
         </is>
       </c>
       <c r="I287" s="4" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="J287" s="6" t="inlineStr"/>
     </row>
@@ -13696,7 +13670,7 @@
         </is>
       </c>
       <c r="I288" s="4" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="J288" s="6" t="inlineStr"/>
     </row>
@@ -13742,7 +13716,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="n">
-        <v>2.35</v>
+        <v>0.72</v>
       </c>
       <c r="J289" s="6" t="inlineStr"/>
     </row>
@@ -13788,7 +13762,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="n">
-        <v>2.68</v>
+        <v>0.77</v>
       </c>
       <c r="J290" s="6" t="inlineStr"/>
     </row>
@@ -13834,7 +13808,7 @@
         </is>
       </c>
       <c r="I291" s="4" t="n">
-        <v>0.93</v>
+        <v>3.32</v>
       </c>
       <c r="J291" s="6" t="inlineStr"/>
     </row>
@@ -13880,7 +13854,7 @@
         </is>
       </c>
       <c r="I292" s="4" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="J292" s="6" t="inlineStr"/>
     </row>
@@ -13926,7 +13900,7 @@
         </is>
       </c>
       <c r="I293" s="4" t="n">
-        <v>3.47</v>
+        <v>2.53</v>
       </c>
       <c r="J293" s="6" t="inlineStr"/>
     </row>
@@ -13972,7 +13946,7 @@
         </is>
       </c>
       <c r="I294" s="4" t="n">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="J294" s="6" t="inlineStr"/>
     </row>
@@ -14018,7 +13992,7 @@
         </is>
       </c>
       <c r="I295" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J295" s="6" t="inlineStr"/>
     </row>
@@ -14064,7 +14038,7 @@
         </is>
       </c>
       <c r="I296" s="4" t="n">
-        <v>2.38</v>
+        <v>3.01</v>
       </c>
       <c r="J296" s="6" t="inlineStr"/>
     </row>
@@ -14110,7 +14084,7 @@
         </is>
       </c>
       <c r="I297" s="4" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="J297" s="6" t="inlineStr"/>
     </row>
@@ -14156,7 +14130,7 @@
         </is>
       </c>
       <c r="I298" s="4" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="J298" s="6" t="inlineStr"/>
     </row>
@@ -14202,7 +14176,7 @@
         </is>
       </c>
       <c r="I299" s="4" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="J299" s="6" t="inlineStr"/>
     </row>
@@ -14248,7 +14222,7 @@
         </is>
       </c>
       <c r="I300" s="4" t="n">
-        <v>1.25</v>
+        <v>2.47</v>
       </c>
       <c r="J300" s="6" t="inlineStr"/>
     </row>
@@ -14294,7 +14268,7 @@
         </is>
       </c>
       <c r="I301" s="4" t="n">
-        <v>3.4</v>
+        <v>0.76</v>
       </c>
       <c r="J301" s="6" t="inlineStr"/>
     </row>
@@ -14340,7 +14314,7 @@
         </is>
       </c>
       <c r="I302" s="4" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="J302" s="6" t="inlineStr"/>
     </row>
@@ -14386,7 +14360,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="J303" s="6" t="inlineStr"/>
     </row>
@@ -14432,7 +14406,7 @@
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="J304" s="6" t="inlineStr"/>
     </row>
@@ -14478,7 +14452,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="J305" s="6" t="inlineStr"/>
     </row>
@@ -14524,7 +14498,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>0.79</v>
+        <v>1.35</v>
       </c>
       <c r="J306" s="6" t="inlineStr"/>
     </row>
@@ -14570,7 +14544,7 @@
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>0.92</v>
+        <v>2.1</v>
       </c>
       <c r="J307" s="6" t="inlineStr"/>
     </row>
@@ -14616,7 +14590,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="n">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="J308" s="6" t="inlineStr"/>
     </row>
@@ -14662,7 +14636,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="n">
-        <v>0.85</v>
+        <v>3.47</v>
       </c>
       <c r="J309" s="6" t="inlineStr"/>
     </row>
@@ -14708,7 +14682,7 @@
         </is>
       </c>
       <c r="I310" s="4" t="n">
-        <v>1.55</v>
+        <v>3.17</v>
       </c>
       <c r="J310" s="6" t="inlineStr"/>
     </row>
@@ -14754,7 +14728,7 @@
         </is>
       </c>
       <c r="I311" s="4" t="n">
-        <v>1.58</v>
+        <v>2.63</v>
       </c>
       <c r="J311" s="6" t="inlineStr"/>
     </row>
@@ -14800,59 +14774,55 @@
         </is>
       </c>
       <c r="I312" s="4" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="J312" s="6" t="inlineStr"/>
     </row>
     <row r="313" ht="15" customHeight="1">
-      <c r="A313" s="7" t="inlineStr">
+      <c r="A313" s="4" t="inlineStr">
         <is>
           <t>AND_UI_030</t>
         </is>
       </c>
-      <c r="B313" s="7" t="inlineStr">
+      <c r="B313" s="4" t="inlineStr">
         <is>
           <t>Android UI</t>
         </is>
       </c>
-      <c r="C313" s="7" t="inlineStr">
+      <c r="C313" s="4" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="D313" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E313" s="8" t="inlineStr">
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
         <is>
           <t>UI/UX check — UI smoke test #30</t>
         </is>
       </c>
-      <c r="F313" s="7" t="inlineStr">
-        <is>
-          <t>Pixel 7 API 33</t>
-        </is>
-      </c>
-      <c r="G313" s="7" t="inlineStr">
-        <is>
-          <t>Android 13</t>
-        </is>
-      </c>
-      <c r="H313" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I313" s="7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J313" s="9" t="inlineStr">
-        <is>
-          <t>Element not found: timeout after 10s</t>
-        </is>
-      </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7 API 33</t>
+        </is>
+      </c>
+      <c r="G313" s="4" t="inlineStr">
+        <is>
+          <t>Android 13</t>
+        </is>
+      </c>
+      <c r="H313" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I313" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J313" s="6" t="inlineStr"/>
     </row>
     <row r="314" ht="15" customHeight="1">
       <c r="A314" s="4" t="inlineStr">
@@ -14896,7 +14866,7 @@
         </is>
       </c>
       <c r="I314" s="4" t="n">
-        <v>1.84</v>
+        <v>3.23</v>
       </c>
       <c r="J314" s="6" t="inlineStr"/>
     </row>
@@ -14942,7 +14912,7 @@
         </is>
       </c>
       <c r="I315" s="4" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="J315" s="6" t="inlineStr"/>
     </row>
@@ -14988,7 +14958,7 @@
         </is>
       </c>
       <c r="I316" s="4" t="n">
-        <v>2.66</v>
+        <v>1.94</v>
       </c>
       <c r="J316" s="6" t="inlineStr"/>
     </row>
@@ -15034,7 +15004,7 @@
         </is>
       </c>
       <c r="I317" s="4" t="n">
-        <v>2.53</v>
+        <v>1.39</v>
       </c>
       <c r="J317" s="6" t="inlineStr"/>
     </row>
@@ -15080,7 +15050,7 @@
         </is>
       </c>
       <c r="I318" s="4" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="J318" s="6" t="inlineStr"/>
     </row>
@@ -15126,7 +15096,7 @@
         </is>
       </c>
       <c r="I319" s="4" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="J319" s="6" t="inlineStr"/>
     </row>
@@ -15172,7 +15142,7 @@
         </is>
       </c>
       <c r="I320" s="4" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="J320" s="6" t="inlineStr"/>
     </row>
@@ -15218,59 +15188,55 @@
         </is>
       </c>
       <c r="I321" s="4" t="n">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="J321" s="6" t="inlineStr"/>
     </row>
     <row r="322" ht="15" customHeight="1">
-      <c r="A322" s="7" t="inlineStr">
+      <c r="A322" s="4" t="inlineStr">
         <is>
           <t>AND_UI_039</t>
         </is>
       </c>
-      <c r="B322" s="7" t="inlineStr">
+      <c r="B322" s="4" t="inlineStr">
         <is>
           <t>Android UI</t>
         </is>
       </c>
-      <c r="C322" s="7" t="inlineStr">
+      <c r="C322" s="4" t="inlineStr">
         <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="D322" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E322" s="8" t="inlineStr">
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>UI/UX check — UI smoke test #39</t>
         </is>
       </c>
-      <c r="F322" s="7" t="inlineStr">
-        <is>
-          <t>Pixel 7 API 33</t>
-        </is>
-      </c>
-      <c r="G322" s="7" t="inlineStr">
-        <is>
-          <t>Android 13</t>
-        </is>
-      </c>
-      <c r="H322" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I322" s="7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J322" s="9" t="inlineStr">
-        <is>
-          <t>Element not found: timeout after 10s</t>
-        </is>
-      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7 API 33</t>
+        </is>
+      </c>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>Android 13</t>
+        </is>
+      </c>
+      <c r="H322" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I322" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J322" s="6" t="inlineStr"/>
     </row>
     <row r="323" ht="15" customHeight="1">
       <c r="A323" s="4" t="inlineStr">
@@ -15314,7 +15280,7 @@
         </is>
       </c>
       <c r="I323" s="4" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="J323" s="6" t="inlineStr"/>
     </row>
@@ -15360,7 +15326,7 @@
         </is>
       </c>
       <c r="I324" s="4" t="n">
-        <v>1.53</v>
+        <v>0.79</v>
       </c>
       <c r="J324" s="6" t="inlineStr"/>
     </row>
@@ -15406,7 +15372,7 @@
         </is>
       </c>
       <c r="I325" s="4" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="J325" s="6" t="inlineStr"/>
     </row>
@@ -15452,7 +15418,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="n">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="J326" s="6" t="inlineStr"/>
     </row>
@@ -15498,7 +15464,7 @@
         </is>
       </c>
       <c r="I327" s="4" t="n">
-        <v>0.57</v>
+        <v>3.43</v>
       </c>
       <c r="J327" s="6" t="inlineStr"/>
     </row>
@@ -15544,7 +15510,7 @@
         </is>
       </c>
       <c r="I328" s="4" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="J328" s="6" t="inlineStr"/>
     </row>
@@ -15590,7 +15556,7 @@
         </is>
       </c>
       <c r="I329" s="4" t="n">
-        <v>2.46</v>
+        <v>1.65</v>
       </c>
       <c r="J329" s="6" t="inlineStr"/>
     </row>
@@ -15636,7 +15602,7 @@
         </is>
       </c>
       <c r="I330" s="4" t="n">
-        <v>0.88</v>
+        <v>2.02</v>
       </c>
       <c r="J330" s="6" t="inlineStr"/>
     </row>
@@ -15682,7 +15648,7 @@
         </is>
       </c>
       <c r="I331" s="4" t="n">
-        <v>1.7</v>
+        <v>2.79</v>
       </c>
       <c r="J331" s="6" t="inlineStr"/>
     </row>
@@ -15728,7 +15694,7 @@
         </is>
       </c>
       <c r="I332" s="4" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="J332" s="6" t="inlineStr"/>
     </row>
@@ -15774,7 +15740,7 @@
         </is>
       </c>
       <c r="I333" s="4" t="n">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="J333" s="6" t="inlineStr"/>
     </row>
@@ -15820,7 +15786,7 @@
         </is>
       </c>
       <c r="I334" s="4" t="n">
-        <v>0.73</v>
+        <v>1.99</v>
       </c>
       <c r="J334" s="6" t="inlineStr"/>
     </row>
@@ -15866,7 +15832,7 @@
         </is>
       </c>
       <c r="I335" s="4" t="n">
-        <v>1.41</v>
+        <v>3.31</v>
       </c>
       <c r="J335" s="6" t="inlineStr"/>
     </row>
@@ -15912,7 +15878,7 @@
         </is>
       </c>
       <c r="I336" s="4" t="n">
-        <v>1</v>
+        <v>3.03</v>
       </c>
       <c r="J336" s="6" t="inlineStr"/>
     </row>
@@ -15958,7 +15924,7 @@
         </is>
       </c>
       <c r="I337" s="4" t="n">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="J337" s="6" t="inlineStr"/>
     </row>
@@ -16004,7 +15970,7 @@
         </is>
       </c>
       <c r="I338" s="4" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="J338" s="6" t="inlineStr"/>
     </row>
@@ -16050,7 +16016,7 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>1.89</v>
+        <v>1.21</v>
       </c>
       <c r="J339" s="6" t="inlineStr"/>
     </row>
@@ -16096,7 +16062,7 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="J340" s="6" t="inlineStr"/>
     </row>
@@ -16142,7 +16108,7 @@
         </is>
       </c>
       <c r="I341" s="4" t="n">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
       <c r="J341" s="6" t="inlineStr"/>
     </row>
@@ -16188,7 +16154,7 @@
         </is>
       </c>
       <c r="I342" s="4" t="n">
-        <v>1.62</v>
+        <v>0.92</v>
       </c>
       <c r="J342" s="6" t="inlineStr"/>
     </row>
@@ -16234,7 +16200,7 @@
         </is>
       </c>
       <c r="I343" s="4" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="J343" s="6" t="inlineStr"/>
     </row>
@@ -16280,7 +16246,7 @@
         </is>
       </c>
       <c r="I344" s="4" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="J344" s="6" t="inlineStr"/>
     </row>
@@ -16326,7 +16292,7 @@
         </is>
       </c>
       <c r="I345" s="4" t="n">
-        <v>1.99</v>
+        <v>2.81</v>
       </c>
       <c r="J345" s="6" t="inlineStr"/>
     </row>
@@ -16372,7 +16338,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="J346" s="6" t="inlineStr"/>
     </row>
@@ -16418,7 +16384,7 @@
         </is>
       </c>
       <c r="I347" s="4" t="n">
-        <v>2.45</v>
+        <v>1.05</v>
       </c>
       <c r="J347" s="6" t="inlineStr"/>
     </row>
@@ -16464,7 +16430,7 @@
         </is>
       </c>
       <c r="I348" s="4" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="J348" s="6" t="inlineStr"/>
     </row>
@@ -16510,7 +16476,7 @@
         </is>
       </c>
       <c r="I349" s="4" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="J349" s="6" t="inlineStr"/>
     </row>
@@ -16556,7 +16522,7 @@
         </is>
       </c>
       <c r="I350" s="4" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="J350" s="6" t="inlineStr"/>
     </row>
@@ -16602,7 +16568,7 @@
         </is>
       </c>
       <c r="I351" s="4" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="J351" s="6" t="inlineStr"/>
     </row>
@@ -16648,7 +16614,7 @@
         </is>
       </c>
       <c r="I352" s="4" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="J352" s="6" t="inlineStr"/>
     </row>
@@ -16694,7 +16660,7 @@
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="J353" s="6" t="inlineStr"/>
     </row>
@@ -16740,7 +16706,7 @@
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="J354" s="6" t="inlineStr"/>
     </row>
@@ -16786,7 +16752,7 @@
         </is>
       </c>
       <c r="I355" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.41</v>
       </c>
       <c r="J355" s="6" t="inlineStr"/>
     </row>
@@ -16832,7 +16798,7 @@
         </is>
       </c>
       <c r="I356" s="4" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
       <c r="J356" s="6" t="inlineStr"/>
     </row>
@@ -16878,7 +16844,7 @@
         </is>
       </c>
       <c r="I357" s="4" t="n">
-        <v>3.37</v>
+        <v>1.83</v>
       </c>
       <c r="J357" s="6" t="inlineStr"/>
     </row>
@@ -16924,7 +16890,7 @@
         </is>
       </c>
       <c r="I358" s="4" t="n">
-        <v>1.01</v>
+        <v>0.83</v>
       </c>
       <c r="J358" s="6" t="inlineStr"/>
     </row>
@@ -16970,7 +16936,7 @@
         </is>
       </c>
       <c r="I359" s="4" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J359" s="6" t="inlineStr"/>
     </row>
@@ -17016,7 +16982,7 @@
         </is>
       </c>
       <c r="I360" s="4" t="n">
-        <v>1.24</v>
+        <v>3.41</v>
       </c>
       <c r="J360" s="6" t="inlineStr"/>
     </row>
@@ -17062,7 +17028,7 @@
         </is>
       </c>
       <c r="I361" s="4" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="J361" s="6" t="inlineStr"/>
     </row>
@@ -17108,7 +17074,7 @@
         </is>
       </c>
       <c r="I362" s="4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J362" s="6" t="inlineStr"/>
     </row>
@@ -17154,7 +17120,7 @@
         </is>
       </c>
       <c r="I363" s="4" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="J363" s="6" t="inlineStr"/>
     </row>
@@ -17200,7 +17166,7 @@
         </is>
       </c>
       <c r="I364" s="4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J364" s="6" t="inlineStr"/>
     </row>
@@ -17246,7 +17212,7 @@
         </is>
       </c>
       <c r="I365" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="J365" s="6" t="inlineStr"/>
     </row>
@@ -17292,7 +17258,7 @@
         </is>
       </c>
       <c r="I366" s="4" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="J366" s="6" t="inlineStr"/>
     </row>
@@ -17338,7 +17304,7 @@
         </is>
       </c>
       <c r="I367" s="4" t="n">
-        <v>1.68</v>
+        <v>3.01</v>
       </c>
       <c r="J367" s="6" t="inlineStr"/>
     </row>
@@ -17384,7 +17350,7 @@
         </is>
       </c>
       <c r="I368" s="4" t="n">
-        <v>1.13</v>
+        <v>2.42</v>
       </c>
       <c r="J368" s="6" t="inlineStr"/>
     </row>
@@ -17430,7 +17396,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="J369" s="6" t="inlineStr"/>
     </row>
@@ -17476,7 +17442,7 @@
         </is>
       </c>
       <c r="I370" s="4" t="n">
-        <v>1.24</v>
+        <v>3.29</v>
       </c>
       <c r="J370" s="6" t="inlineStr"/>
     </row>
@@ -17522,7 +17488,7 @@
         </is>
       </c>
       <c r="I371" s="4" t="n">
-        <v>2.04</v>
+        <v>3.36</v>
       </c>
       <c r="J371" s="6" t="inlineStr"/>
     </row>
@@ -17568,7 +17534,7 @@
         </is>
       </c>
       <c r="I372" s="4" t="n">
-        <v>3.26</v>
+        <v>2.13</v>
       </c>
       <c r="J372" s="6" t="inlineStr"/>
     </row>
@@ -17614,7 +17580,7 @@
         </is>
       </c>
       <c r="I373" s="4" t="n">
-        <v>2.4</v>
+        <v>0.71</v>
       </c>
       <c r="J373" s="6" t="inlineStr"/>
     </row>
@@ -17660,7 +17626,7 @@
         </is>
       </c>
       <c r="I374" s="4" t="n">
-        <v>3.37</v>
+        <v>2.89</v>
       </c>
       <c r="J374" s="6" t="inlineStr"/>
     </row>
@@ -17706,7 +17672,7 @@
         </is>
       </c>
       <c r="I375" s="4" t="n">
-        <v>0.66</v>
+        <v>2.18</v>
       </c>
       <c r="J375" s="6" t="inlineStr"/>
     </row>
@@ -17752,7 +17718,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="J376" s="6" t="inlineStr"/>
     </row>
@@ -17798,7 +17764,7 @@
         </is>
       </c>
       <c r="I377" s="4" t="n">
-        <v>3.39</v>
+        <v>2.05</v>
       </c>
       <c r="J377" s="6" t="inlineStr"/>
     </row>
@@ -17844,7 +17810,7 @@
         </is>
       </c>
       <c r="I378" s="4" t="n">
-        <v>1.43</v>
+        <v>2.61</v>
       </c>
       <c r="J378" s="6" t="inlineStr"/>
     </row>
@@ -17890,7 +17856,7 @@
         </is>
       </c>
       <c r="I379" s="4" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="J379" s="6" t="inlineStr"/>
     </row>
@@ -17936,7 +17902,7 @@
         </is>
       </c>
       <c r="I380" s="4" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="J380" s="6" t="inlineStr"/>
     </row>
@@ -17982,7 +17948,7 @@
         </is>
       </c>
       <c r="I381" s="4" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="J381" s="6" t="inlineStr"/>
     </row>
@@ -18028,7 +17994,7 @@
         </is>
       </c>
       <c r="I382" s="4" t="n">
-        <v>2.78</v>
+        <v>0.85</v>
       </c>
       <c r="J382" s="6" t="inlineStr"/>
     </row>
@@ -18074,59 +18040,55 @@
         </is>
       </c>
       <c r="I383" s="4" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="J383" s="6" t="inlineStr"/>
     </row>
     <row r="384" ht="15" customHeight="1">
-      <c r="A384" s="7" t="inlineStr">
+      <c r="A384" s="4" t="inlineStr">
         <is>
           <t>AND_PERF_041</t>
         </is>
       </c>
-      <c r="B384" s="7" t="inlineStr">
+      <c r="B384" s="4" t="inlineStr">
         <is>
           <t>Android Performance</t>
         </is>
       </c>
-      <c r="C384" s="7" t="inlineStr">
+      <c r="C384" s="4" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D384" s="7" t="inlineStr">
+      <c r="D384" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E384" s="8" t="inlineStr">
+      <c r="E384" s="5" t="inlineStr">
         <is>
           <t>Performance benchmark #41</t>
         </is>
       </c>
-      <c r="F384" s="7" t="inlineStr">
-        <is>
-          <t>Pixel 7 API 33</t>
-        </is>
-      </c>
-      <c r="G384" s="7" t="inlineStr">
-        <is>
-          <t>Android 13</t>
-        </is>
-      </c>
-      <c r="H384" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I384" s="7" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J384" s="9" t="inlineStr">
-        <is>
-          <t>Element not found: timeout after 10s</t>
-        </is>
-      </c>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7 API 33</t>
+        </is>
+      </c>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>Android 13</t>
+        </is>
+      </c>
+      <c r="H384" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I384" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J384" s="6" t="inlineStr"/>
     </row>
     <row r="385" ht="15" customHeight="1">
       <c r="A385" s="4" t="inlineStr">
@@ -18170,7 +18132,7 @@
         </is>
       </c>
       <c r="I385" s="4" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="J385" s="6" t="inlineStr"/>
     </row>
@@ -18216,7 +18178,7 @@
         </is>
       </c>
       <c r="I386" s="4" t="n">
-        <v>2.44</v>
+        <v>1.6</v>
       </c>
       <c r="J386" s="6" t="inlineStr"/>
     </row>
@@ -18262,7 +18224,7 @@
         </is>
       </c>
       <c r="I387" s="4" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="J387" s="6" t="inlineStr"/>
     </row>
@@ -18308,7 +18270,7 @@
         </is>
       </c>
       <c r="I388" s="4" t="n">
-        <v>0.71</v>
+        <v>1.77</v>
       </c>
       <c r="J388" s="6" t="inlineStr"/>
     </row>
@@ -18354,7 +18316,7 @@
         </is>
       </c>
       <c r="I389" s="4" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="J389" s="6" t="inlineStr"/>
     </row>
@@ -18400,7 +18362,7 @@
         </is>
       </c>
       <c r="I390" s="4" t="n">
-        <v>1.99</v>
+        <v>3.29</v>
       </c>
       <c r="J390" s="6" t="inlineStr"/>
     </row>
@@ -18446,7 +18408,7 @@
         </is>
       </c>
       <c r="I391" s="4" t="n">
-        <v>2.51</v>
+        <v>3.35</v>
       </c>
       <c r="J391" s="6" t="inlineStr"/>
     </row>
@@ -18492,7 +18454,7 @@
         </is>
       </c>
       <c r="I392" s="4" t="n">
-        <v>0.83</v>
+        <v>1.74</v>
       </c>
       <c r="J392" s="6" t="inlineStr"/>
     </row>
@@ -18538,7 +18500,7 @@
         </is>
       </c>
       <c r="I393" s="4" t="n">
-        <v>1.55</v>
+        <v>3.31</v>
       </c>
       <c r="J393" s="6" t="inlineStr"/>
     </row>
@@ -18584,7 +18546,7 @@
         </is>
       </c>
       <c r="I394" s="4" t="n">
-        <v>0.93</v>
+        <v>1.68</v>
       </c>
       <c r="J394" s="6" t="inlineStr"/>
     </row>
@@ -18630,7 +18592,7 @@
         </is>
       </c>
       <c r="I395" s="4" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="J395" s="6" t="inlineStr"/>
     </row>
@@ -18676,7 +18638,7 @@
         </is>
       </c>
       <c r="I396" s="4" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="J396" s="6" t="inlineStr"/>
     </row>
@@ -18722,7 +18684,7 @@
         </is>
       </c>
       <c r="I397" s="4" t="n">
-        <v>3.41</v>
+        <v>0.86</v>
       </c>
       <c r="J397" s="6" t="inlineStr"/>
     </row>
@@ -18768,7 +18730,7 @@
         </is>
       </c>
       <c r="I398" s="4" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="J398" s="6" t="inlineStr"/>
     </row>
@@ -18814,7 +18776,7 @@
         </is>
       </c>
       <c r="I399" s="4" t="n">
-        <v>1.62</v>
+        <v>0.6</v>
       </c>
       <c r="J399" s="6" t="inlineStr"/>
     </row>
@@ -18860,7 +18822,7 @@
         </is>
       </c>
       <c r="I400" s="4" t="n">
-        <v>0.85</v>
+        <v>2.91</v>
       </c>
       <c r="J400" s="6" t="inlineStr"/>
     </row>
@@ -18906,7 +18868,7 @@
         </is>
       </c>
       <c r="I401" s="4" t="n">
-        <v>0.54</v>
+        <v>2.61</v>
       </c>
       <c r="J401" s="6" t="inlineStr"/>
     </row>
@@ -18952,7 +18914,7 @@
         </is>
       </c>
       <c r="I402" s="4" t="n">
-        <v>2.63</v>
+        <v>1.46</v>
       </c>
       <c r="J402" s="6" t="inlineStr"/>
     </row>
@@ -18998,7 +18960,7 @@
         </is>
       </c>
       <c r="I403" s="4" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="J403" s="6" t="inlineStr"/>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 09:15</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 03:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 03:50</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 04:01</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 04:01</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 04:03</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 04:03</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 04:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 04:13</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:15</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:15</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:17</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:17</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:27</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:27</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:39</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-29 06:39</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-30 06:35</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-30 06:35</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-31 06:51</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-07-31 06:51</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-01 06:36</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-01 06:36</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-02 06:40</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-02 06:40</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-03 07:37</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-03 07:37</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-04 06:35</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-04 06:35</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-05 06:36</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-05 06:36</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-06 06:39</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-06 06:39</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-07 05:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-07 05:47</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-08 05:05</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-08 05:05</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-09 05:12</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-09 05:12</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-10 05:39</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-10 05:39</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-11 05:15</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-11 05:15</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-12 05:42</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-12 05:42</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-13 05:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-13 05:45</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-14 05:42</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-14 05:42</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-15 04:38</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-15 04:38</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-16 04:42</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-16 04:42</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-17 04:52</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-17 04:52</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-18 04:43</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-18 04:43</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-19 04:44</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-19 04:44</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-20 04:44</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-20 04:44</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-21 04:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-21 04:47</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-22 04:41</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-22 04:41</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-23 04:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-23 04:45</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-24 04:54</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-24 04:54</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-25 04:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-25 04:47</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-26 04:48</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-26 04:48</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-27 15:07</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-27 15:07</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-28 16:30</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-28 16:30</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-29 10:59</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-29 10:59</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-30 09:52</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-30 09:52</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-31 10:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-08-31 10:45</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-01 09:20</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-01 09:20</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-02 08:41</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-02 08:41</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-03 08:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-03 08:50</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-04 08:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-04 08:45</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-05 08:16</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-05 08:16</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-06 08:35</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-06 08:35</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-07 09:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-07 09:13</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-08 08:47</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-08 08:47</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-09 08:53</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-09 08:53</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-10 08:52</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-10 08:52</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-11 08:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Android/Android_Appium_Report_LATEST.xlsx
+++ b/Test Results/Android/Android_Appium_Report_LATEST.xlsx
@@ -508,7 +508,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-11 08:50</t>
+          <t>Total: 400  |  Passed: 400  |  Failed: 0  |  Pass Rate: 100.0%  |  Date: 2026-09-12 08:33</t>
         </is>
       </c>
     </row>
